--- a/public/system/export/inventoryaudit.xlsx
+++ b/public/system/export/inventoryaudit.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sổ kiểm kê" sheetId="2" r:id="rId1"/>
+    <sheet name="Phiếu báo cáo" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>SỞ GD&amp;ĐT ...</t>
   </si>
@@ -85,13 +86,31 @@
   </si>
   <si>
     <t>Mã phiếu</t>
+  </si>
+  <si>
+    <t>PHIẾU BÁO CÁO KIỂM KÊ THIẾT BỊ</t>
+  </si>
+  <si>
+    <t>SỐ LƯỢNG  THEO SỔ TÀI SẢN</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>Thành tiền</t>
+  </si>
+  <si>
+    <t>Hiện có tại thời điểm kiểm kê</t>
+  </si>
+  <si>
+    <t>TÊN THIẾT BỊ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -129,6 +148,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -138,7 +165,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -187,11 +214,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -205,34 +311,73 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -460,148 +605,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="G1" s="7" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="G1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="4" spans="1:13" ht="18">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="I6" s="12" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="I6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="I7" s="12" t="s">
+      <c r="C7" s="7"/>
+      <c r="I7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="10" t="s">
+      <c r="I9" s="15"/>
+      <c r="J9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="13"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
       <c r="L11" s="3" t="s">
         <v>11</v>
       </c>
@@ -611,8 +756,8 @@
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -626,8 +771,8 @@
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -641,8 +786,8 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -656,8 +801,8 @@
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -671,8 +816,8 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -686,8 +831,8 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -701,8 +846,8 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -716,8 +861,8 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -731,8 +876,8 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -746,8 +891,8 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -761,23 +906,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="G2:M2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B9:C11"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
@@ -792,6 +920,339 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="G2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="G1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="I6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="I7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" spans="1:12" ht="24">
+      <c r="A10" s="8"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="1"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="1"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="1"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="1"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="1"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
